--- a/data/market-sweeps/Germany.xlsx
+++ b/data/market-sweeps/Germany.xlsx
@@ -106,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -123,6 +123,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E375"/>
+  <dimension ref="A1:F375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -524,6 +525,11 @@
           <t>exchange</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>isin</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -551,6 +557,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F2" s="8" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -578,6 +585,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -605,6 +613,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -632,6 +641,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -659,6 +669,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -686,6 +697,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -713,6 +725,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -740,6 +753,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -767,6 +781,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -794,6 +809,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -821,6 +837,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -848,6 +865,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -875,6 +893,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -902,6 +921,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -929,6 +949,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -956,6 +977,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -983,6 +1005,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1010,6 +1033,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1037,6 +1061,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1064,6 +1089,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1091,6 +1117,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1118,6 +1145,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1145,6 +1173,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1172,6 +1201,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1199,6 +1229,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1226,6 +1257,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1253,6 +1285,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1280,6 +1313,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1307,6 +1341,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1334,6 +1369,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1361,6 +1397,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1388,6 +1425,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1415,6 +1453,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1442,6 +1481,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1469,6 +1509,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1496,6 +1537,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1523,6 +1565,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1550,6 +1593,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1577,6 +1621,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1604,6 +1649,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1631,6 +1677,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -1658,6 +1705,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1685,6 +1733,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F44" s="8" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1712,6 +1761,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F45" s="8" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1739,6 +1789,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1766,6 +1817,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1793,6 +1845,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -1820,6 +1873,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1847,6 +1901,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1874,6 +1929,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F51" s="8" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1901,6 +1957,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1928,6 +1985,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F53" s="8" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1955,6 +2013,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1982,6 +2041,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2009,6 +2069,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -2036,6 +2097,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2063,6 +2125,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F58" s="8" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -2090,6 +2153,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F59" s="8" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2117,6 +2181,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F60" s="8" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -2144,6 +2209,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2171,6 +2237,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -2198,6 +2265,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2225,6 +2293,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2252,6 +2321,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2279,6 +2349,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -2306,6 +2377,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2333,6 +2405,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -2360,6 +2433,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2387,6 +2461,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -2414,6 +2489,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2441,6 +2517,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F72" s="8" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -2468,6 +2545,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2495,6 +2573,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F74" s="8" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -2522,6 +2601,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2549,6 +2629,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -2576,6 +2657,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2603,6 +2685,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -2630,6 +2713,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F79" s="8" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2657,6 +2741,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F80" s="8" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -2684,6 +2769,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F81" s="8" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2711,6 +2797,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -2738,6 +2825,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F83" s="8" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2765,6 +2853,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -2792,6 +2881,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2819,6 +2909,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -2846,6 +2937,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2873,6 +2965,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F88" s="8" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -2900,6 +2993,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F89" s="8" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2927,6 +3021,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F90" s="8" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -2954,6 +3049,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2981,6 +3077,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -3008,6 +3105,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F93" s="8" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3035,6 +3133,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F94" s="8" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -3062,6 +3161,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F95" s="8" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3089,6 +3189,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F96" s="8" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -3116,6 +3217,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F97" s="8" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3143,6 +3245,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -3170,6 +3273,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3197,6 +3301,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F100" s="8" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -3224,6 +3329,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F101" s="8" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3251,6 +3357,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F102" s="8" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -3278,6 +3385,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F103" s="8" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3305,6 +3413,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F104" s="8" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -3332,6 +3441,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3359,6 +3469,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F106" s="8" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -3386,6 +3497,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F107" s="8" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -3413,6 +3525,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F108" s="8" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -3440,6 +3553,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F109" s="8" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -3467,6 +3581,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F110" s="8" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -3494,6 +3609,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F111" s="8" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -3521,6 +3637,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F112" s="8" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -3548,6 +3665,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F113" s="8" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -3575,6 +3693,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F114" s="8" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -3602,6 +3721,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F115" s="8" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -3629,6 +3749,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F116" s="8" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -3656,6 +3777,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F117" s="8" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -3683,6 +3805,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F118" s="8" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -3710,6 +3833,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3737,6 +3861,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F120" s="8" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -3764,6 +3889,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F121" s="8" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3791,6 +3917,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F122" s="8" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -3818,6 +3945,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F123" s="8" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -3845,6 +3973,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F124" s="8" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -3872,6 +4001,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F125" s="8" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3899,6 +4029,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F126" s="8" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -3926,6 +4057,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F127" s="8" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -3953,6 +4085,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F128" s="8" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -3980,6 +4113,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F129" s="8" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -4007,6 +4141,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F130" s="8" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -4034,6 +4169,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F131" s="8" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -4061,6 +4197,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F132" s="8" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -4088,6 +4225,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F133" s="8" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -4115,6 +4253,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F134" s="8" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -4142,6 +4281,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F135" s="8" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -4169,6 +4309,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F136" s="8" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -4196,6 +4337,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F137" s="8" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -4223,6 +4365,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F138" s="8" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -4250,6 +4393,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F139" s="8" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -4277,6 +4421,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F140" s="8" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -4304,6 +4449,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F141" s="8" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -4331,6 +4477,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F142" s="8" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -4358,6 +4505,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F143" s="8" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -4385,6 +4533,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F144" s="8" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -4412,6 +4561,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F145" s="8" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -4439,6 +4589,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F146" s="8" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -4466,6 +4617,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F147" s="8" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -4493,6 +4645,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F148" s="8" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -4520,6 +4673,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F149" s="8" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -4547,6 +4701,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F150" s="8" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -4574,6 +4729,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F151" s="8" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -4601,6 +4757,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F152" s="8" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -4628,6 +4785,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F153" s="8" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -4655,6 +4813,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F154" s="8" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
@@ -4682,6 +4841,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F155" s="8" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -4709,6 +4869,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F156" s="8" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -4736,6 +4897,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F157" s="8" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -4763,6 +4925,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F158" s="8" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -4790,6 +4953,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F159" s="8" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -4817,6 +4981,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F160" s="8" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -4844,6 +5009,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F161" s="8" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -4871,6 +5037,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F162" s="8" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -4898,6 +5065,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F163" s="8" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -4925,6 +5093,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F164" s="8" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -4952,6 +5121,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F165" s="8" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -4979,6 +5149,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F166" s="8" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -5006,6 +5177,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F167" s="8" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -5033,6 +5205,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F168" s="8" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
@@ -5060,6 +5233,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F169" s="8" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -5087,6 +5261,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F170" s="8" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -5114,6 +5289,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F171" s="8" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -5141,6 +5317,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F172" s="8" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -5168,6 +5345,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F173" s="8" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -5195,6 +5373,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F174" s="8" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -5222,6 +5401,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F175" s="8" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -5249,6 +5429,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F176" s="8" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -5276,6 +5457,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F177" s="8" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -5303,6 +5485,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F178" s="8" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -5330,6 +5513,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F179" s="8" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -5357,6 +5541,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F180" s="8" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -5384,6 +5569,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F181" s="8" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -5411,6 +5597,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F182" s="8" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -5438,6 +5625,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F183" s="8" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -5465,6 +5653,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F184" s="8" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -5492,6 +5681,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F185" s="8" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -5519,6 +5709,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F186" s="8" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -5546,6 +5737,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F187" s="8" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -5573,6 +5765,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F188" s="8" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
@@ -5600,6 +5793,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F189" s="8" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -5627,6 +5821,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F190" s="8" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -5654,6 +5849,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F191" s="8" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -5681,6 +5877,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F192" s="8" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -5708,6 +5905,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F193" s="8" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -5735,6 +5933,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F194" s="8" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -5762,6 +5961,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F195" s="8" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -5789,6 +5989,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F196" s="8" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -5816,6 +6017,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F197" s="8" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -5843,6 +6045,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F198" s="8" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -5870,6 +6073,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F199" s="8" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -5897,6 +6101,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F200" s="8" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -5924,6 +6129,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F201" s="8" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -5951,6 +6157,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F202" s="8" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
@@ -5978,6 +6185,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F203" s="8" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -6005,6 +6213,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F204" s="8" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -6032,6 +6241,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F205" s="8" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -6059,6 +6269,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F206" s="8" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -6086,6 +6297,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F207" s="8" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -6113,6 +6325,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F208" s="8" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -6140,6 +6353,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F209" s="8" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -6167,6 +6381,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F210" s="8" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
@@ -6194,6 +6409,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F211" s="8" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -6221,6 +6437,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F212" s="8" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -6248,6 +6465,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F213" s="8" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -6275,6 +6493,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F214" s="8" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -6302,6 +6521,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F215" s="8" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -6329,6 +6549,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F216" s="8" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
@@ -6356,6 +6577,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F217" s="8" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -6383,6 +6605,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F218" s="8" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -6410,6 +6633,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F219" s="8" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -6437,6 +6661,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F220" s="8" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -6464,6 +6689,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F221" s="8" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -6491,6 +6717,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F222" s="8" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -6518,6 +6745,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F223" s="8" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -6545,6 +6773,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F224" s="8" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
@@ -6572,6 +6801,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F225" s="8" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -6599,6 +6829,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F226" s="8" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -6626,6 +6857,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F227" s="8" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -6653,6 +6885,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F228" s="8" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -6680,6 +6913,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F229" s="8" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -6707,6 +6941,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F230" s="8" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
@@ -6734,6 +6969,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F231" s="8" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -6761,6 +6997,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F232" s="8" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -6788,6 +7025,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F233" s="8" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -6815,6 +7053,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F234" s="8" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -6842,6 +7081,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F235" s="8" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -6869,6 +7109,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F236" s="8" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -6896,6 +7137,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F237" s="8" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -6923,6 +7165,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F238" s="8" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
@@ -6950,6 +7193,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F239" s="8" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -6977,6 +7221,7 @@
           <t>FWB - Prime Standard</t>
         </is>
       </c>
+      <c r="F240" s="8" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -7004,6 +7249,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F241" s="8" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -7031,6 +7277,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F242" s="8" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -7058,6 +7305,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F243" s="8" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -7085,6 +7333,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F244" s="8" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
@@ -7112,6 +7361,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F245" s="8" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -7139,6 +7389,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F246" s="8" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -7166,6 +7417,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F247" s="8" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -7193,6 +7445,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F248" s="8" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
@@ -7220,6 +7473,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F249" s="8" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -7247,6 +7501,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F250" s="8" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
@@ -7274,6 +7529,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F251" s="8" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -7301,6 +7557,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F252" s="8" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
@@ -7328,6 +7585,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F253" s="8" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -7355,6 +7613,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F254" s="8" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
@@ -7382,6 +7641,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F255" s="8" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -7409,6 +7669,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F256" s="8" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
@@ -7436,6 +7697,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F257" s="8" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -7463,6 +7725,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F258" s="8" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
@@ -7490,6 +7753,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F259" s="8" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -7517,6 +7781,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F260" s="8" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -7544,6 +7809,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F261" s="8" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -7571,6 +7837,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F262" s="8" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
@@ -7598,6 +7865,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F263" s="8" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -7625,6 +7893,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F264" s="8" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
@@ -7652,6 +7921,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F265" s="8" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -7679,6 +7949,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F266" s="8" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
@@ -7706,6 +7977,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F267" s="8" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -7733,6 +8005,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F268" s="8" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
@@ -7760,6 +8033,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F269" s="8" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -7787,6 +8061,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F270" s="8" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
@@ -7814,6 +8089,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F271" s="8" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -7841,6 +8117,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F272" s="8" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
@@ -7868,6 +8145,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F273" s="8" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -7895,6 +8173,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F274" s="8" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
@@ -7922,6 +8201,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F275" s="8" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -7949,6 +8229,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F276" s="8" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
@@ -7976,6 +8257,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F277" s="8" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -8003,6 +8285,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F278" s="8" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
@@ -8030,6 +8313,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F279" s="8" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -8057,6 +8341,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F280" s="8" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
@@ -8084,6 +8369,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F281" s="8" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -8111,6 +8397,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F282" s="8" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
@@ -8138,6 +8425,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F283" s="8" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -8165,6 +8453,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F284" s="8" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
@@ -8192,6 +8481,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F285" s="8" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -8219,6 +8509,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F286" s="8" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
@@ -8246,6 +8537,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F287" s="8" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -8273,6 +8565,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F288" s="8" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
@@ -8300,6 +8593,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F289" s="8" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -8327,6 +8621,7 @@
           <t>FWB - General Standard</t>
         </is>
       </c>
+      <c r="F290" s="8" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
@@ -8354,6 +8649,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F291" s="8" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -8381,6 +8677,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F292" s="8" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
@@ -8408,6 +8705,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F293" s="8" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -8435,6 +8733,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F294" s="8" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
@@ -8462,6 +8761,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F295" s="8" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -8489,6 +8789,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F296" s="8" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
@@ -8516,6 +8817,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F297" s="8" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -8543,6 +8845,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F298" s="8" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
@@ -8570,6 +8873,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F299" s="8" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -8597,6 +8901,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F300" s="8" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
@@ -8624,6 +8929,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F301" s="8" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -8651,6 +8957,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F302" s="8" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
@@ -8678,6 +8985,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F303" s="8" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -8705,6 +9013,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F304" s="8" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
@@ -8732,6 +9041,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F305" s="8" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -8759,6 +9069,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F306" s="8" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
@@ -8786,6 +9097,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F307" s="8" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -8813,6 +9125,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F308" s="8" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
@@ -8840,6 +9153,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F309" s="8" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -8867,6 +9181,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F310" s="8" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
@@ -8894,6 +9209,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F311" s="8" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -8921,6 +9237,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F312" s="8" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
@@ -8948,6 +9265,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F313" s="8" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -8975,6 +9293,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F314" s="8" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
@@ -9002,6 +9321,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F315" s="8" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -9029,6 +9349,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F316" s="8" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
@@ -9056,6 +9377,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F317" s="8" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -9083,6 +9405,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F318" s="8" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
@@ -9110,6 +9433,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F319" s="8" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -9137,6 +9461,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F320" s="8" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
@@ -9164,6 +9489,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F321" s="8" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -9191,6 +9517,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F322" s="8" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
@@ -9218,6 +9545,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F323" s="8" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -9245,6 +9573,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F324" s="8" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
@@ -9272,6 +9601,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F325" s="8" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -9299,6 +9629,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F326" s="8" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
@@ -9326,6 +9657,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F327" s="8" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -9353,6 +9685,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F328" s="8" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
@@ -9380,6 +9713,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F329" s="8" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -9407,6 +9741,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F330" s="8" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
@@ -9434,6 +9769,7 @@
           <t>FWB - Scale</t>
         </is>
       </c>
+      <c r="F331" s="8" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -9461,6 +9797,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F332" s="8" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
@@ -9488,6 +9825,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F333" s="8" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -9515,6 +9853,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F334" s="8" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
@@ -9542,6 +9881,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F335" s="8" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -9569,6 +9909,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F336" s="8" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
@@ -9596,6 +9937,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F337" s="8" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -9623,6 +9965,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F338" s="8" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
@@ -9650,6 +9993,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F339" s="8" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -9677,6 +10021,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F340" s="8" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
@@ -9704,6 +10049,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F341" s="8" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -9731,6 +10077,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F342" s="8" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
@@ -9758,6 +10105,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F343" s="8" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -9785,6 +10133,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F344" s="8" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
@@ -9812,6 +10161,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F345" s="8" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -9839,6 +10189,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F346" s="8" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
@@ -9866,6 +10217,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F347" s="8" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -9893,6 +10245,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F348" s="8" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
@@ -9920,6 +10273,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F349" s="8" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -9947,6 +10301,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F350" s="8" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
@@ -9974,6 +10329,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F351" s="8" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -10001,6 +10357,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F352" s="8" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
@@ -10028,6 +10385,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F353" s="8" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -10055,6 +10413,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F354" s="8" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
@@ -10082,6 +10441,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F355" s="8" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -10109,6 +10469,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F356" s="8" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
@@ -10136,6 +10497,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F357" s="8" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -10163,6 +10525,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F358" s="8" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
@@ -10190,6 +10553,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F359" s="8" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -10217,6 +10581,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F360" s="8" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
@@ -10244,6 +10609,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F361" s="8" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -10271,6 +10637,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F362" s="8" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
@@ -10298,6 +10665,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F363" s="8" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -10325,6 +10693,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F364" s="8" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
@@ -10352,6 +10721,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F365" s="8" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -10379,6 +10749,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F366" s="8" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
@@ -10406,6 +10777,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F367" s="8" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -10433,6 +10805,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F368" s="8" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
@@ -10460,6 +10833,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F369" s="8" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -10487,6 +10861,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F370" s="8" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
@@ -10514,6 +10889,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F371" s="8" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -10541,6 +10917,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F372" s="8" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
@@ -10568,6 +10945,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F373" s="8" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -10595,6 +10973,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F374" s="8" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
@@ -10622,6 +11001,7 @@
           <t>FWB - Basic Board</t>
         </is>
       </c>
+      <c r="F375" s="8" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E375"/>
